--- a/LubanConfig/Moba/Production/Datas/moba-buff-hud.xlsx
+++ b/LubanConfig/Moba/Production/Datas/moba-buff-hud.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,27 @@
         <v>1</v>
       </c>
       <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>10020001</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Xiao Qiao Skill Hit Speed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
